--- a/brt_config_files/current_config/data/scenario1/traffic_metrics_results.xlsx
+++ b/brt_config_files/current_config/data/scenario1/traffic_metrics_results.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:58:17</t>
+          <t>2026-07-28 23:06:35</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>226.27</v>
+        <v>227.62</v>
       </c>
     </row>
     <row r="4">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13576</v>
+        <v>13657</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>12.27</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="9">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>22.43</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="10">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>22.14</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="11">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -707,22 +707,22 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>35.376</v>
+        <v>35.384</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25.2</v>
+        <v>24.7</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.4591</v>
+        <v>0.4797</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6.049</v>
+        <v>3.908</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -751,22 +751,22 @@
         <v>370</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>25.49</v>
+        <v>23.4</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.4401</v>
+        <v>0.5324</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7.3612</v>
+        <v>4.6433</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -795,22 +795,22 @@
         <v>730</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>25.27</v>
+        <v>24.59</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.4644</v>
+        <v>0.4838</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.9179</v>
+        <v>5.714</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -839,22 +839,22 @@
         <v>1090</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>35.376</v>
+        <v>35.38</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.01</v>
+        <v>23.62</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.5203</v>
+        <v>0.5314</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8.370799999999999</v>
+        <v>9.016</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -883,22 +883,22 @@
         <v>1450</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>35.376</v>
+        <v>35.372</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23.33</v>
+        <v>22.93</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.4872</v>
+        <v>0.5455</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.9722</v>
+        <v>6.5311</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -927,22 +927,22 @@
         <v>1810</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>35.384</v>
+        <v>35.372</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>24.77</v>
+        <v>22.79</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.4673</v>
+        <v>0.5915</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.6778</v>
+        <v>9.3529</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -971,22 +971,22 @@
         <v>2170</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35.384</v>
+        <v>35.376</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24.44</v>
+        <v>22.9</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.4997</v>
+        <v>0.5779</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.1784</v>
+        <v>10.1424</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
         <v>2530</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>35.384</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>24.01</v>
+        <v>23.51</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.5057</v>
+        <v>0.5374</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8.2553</v>
+        <v>6.4833</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -1059,22 +1059,22 @@
         <v>2890</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>35.374</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>24.66</v>
+        <v>22.82</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.4638</v>
+        <v>0.5614</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.8464</v>
+        <v>4.6868</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -1103,22 +1103,22 @@
         <v>3250</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>25.16</v>
+        <v>23.65</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.4686</v>
+        <v>0.5303</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4.9531</v>
+        <v>5.8102</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
         <v>40</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>35.384</v>
+        <v>35.372</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>25.09</v>
+        <v>24.59</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.625</v>
+        <v>0.6476</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5.1555</v>
+        <v>7.0011</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1191,22 +1191,22 @@
         <v>420</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>35.376</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>25.52</v>
+        <v>23.69</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.595</v>
+        <v>0.6901</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5.8109</v>
+        <v>2.916</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1235,22 +1235,22 @@
         <v>750</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>24.98</v>
+        <v>24.3</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.6337</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.1211</v>
+        <v>5.3368</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1279,22 +1279,22 @@
         <v>1130</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>35.384</v>
+        <v>35.372</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>24.26</v>
+        <v>23.54</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.6758</v>
+        <v>0.6891</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5.7953</v>
+        <v>6.523</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1323,22 +1323,22 @@
         <v>1470</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>35.384</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23.54</v>
+        <v>23.18</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.6824</v>
+        <v>0.7208</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.5654</v>
+        <v>5.769</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1367,22 +1367,22 @@
         <v>1840</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>35.372</v>
+        <v>35.374</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>24.66</v>
+        <v>22.86</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.6471</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6.7663</v>
+        <v>5.6219</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1411,22 +1411,22 @@
         <v>2220</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>35.372</v>
+        <v>35.374</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24.16</v>
+        <v>22.93</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7393</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7.8364</v>
+        <v>7.0245</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1455,22 +1455,22 @@
         <v>2560</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>24.44</v>
+        <v>23.51</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.6698</v>
+        <v>0.7033</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.794</v>
+        <v>3.185</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1499,22 +1499,22 @@
         <v>2940</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>24.73</v>
+        <v>23.08</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.5826</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.9101</v>
+        <v>4.8572</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1543,22 +1543,22 @@
         <v>3270</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>24.73</v>
+        <v>23.76</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.6355</v>
+        <v>0.6987</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.4661</v>
+        <v>6.6506</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
         <v>80</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>25.06</v>
+        <v>24.62</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.6273</v>
+        <v>0.646</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.4465</v>
+        <v>6.959</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1631,22 +1631,22 @@
         <v>460</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>35.384</v>
+        <v>35.372</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>25.38</v>
+        <v>23.72</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.5974</v>
+        <v>0.695</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.9849</v>
+        <v>7.2737</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1675,22 +1675,22 @@
         <v>790</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>35.372</v>
+        <v>35.384</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>24.66</v>
+        <v>24.48</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.6342</v>
+        <v>0.6561</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.9212</v>
+        <v>5.0644</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1719,22 +1719,22 @@
         <v>1170</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>35.38</v>
+        <v>35.374</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>24.05</v>
+        <v>23.72</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.6722</v>
+        <v>0.6879</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.4305</v>
+        <v>6.3539</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1763,22 +1763,22 @@
         <v>1510</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>23.8</v>
+        <v>23.08</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.7005</v>
+        <v>0.7248</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.6404</v>
+        <v>6.8284</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1807,22 +1807,22 @@
         <v>1890</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>24.66</v>
+        <v>22.75</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.6432</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5.5785</v>
+        <v>8.3218</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1851,22 +1851,22 @@
         <v>2260</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>35.384</v>
+        <v>35.372</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>24.41</v>
+        <v>22.9</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.6562</v>
+        <v>0.7406</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5.0195</v>
+        <v>6.985</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1895,22 +1895,22 @@
         <v>2600</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>24.44</v>
+        <v>23.33</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.6671</v>
+        <v>0.7064</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.2541</v>
+        <v>5.1696</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -1939,22 +1939,22 @@
         <v>2980</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>24.62</v>
+        <v>23.08</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.7279</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>5.9906</v>
+        <v>2.0399</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -1983,22 +1983,22 @@
         <v>3310</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>24.95</v>
+        <v>23.4</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.62</v>
+        <v>0.7012</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6.3528</v>
+        <v>3.6713</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>17.68</v>
+        <v>17.5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>20.71</v>
+        <v>20.38</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>530</v>
@@ -2079,17 +2079,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>11738852154</t>
+          <t>4697920632</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.09</v>
+        <v>4.24</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.96</v>
+        <v>5.04</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -2100,17 +2100,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>4697920632</t>
+          <t>11738852154</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.28</v>
+        <v>3.26</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5.12</v>
+        <v>3.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -2121,17 +2121,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3478050366</t>
+          <t>1247664987</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -2142,17 +2142,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3478026415</t>
+          <t>2512738712</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -2163,17 +2163,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1247664987</t>
+          <t>3478026415</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -2184,17 +2184,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2512738712</t>
+          <t>3478050366</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -2209,13 +2209,13 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>462</v>
+        <v>548</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2247,17 +2247,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1785959154</t>
+          <t>1833486490</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2268,17 +2268,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>13134580211</t>
+          <t>11516632600</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -2289,17 +2289,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2271259942</t>
+          <t>13134580211</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -2310,17 +2310,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>3663535282</t>
+          <t>12238461185</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -2331,17 +2331,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1833486490</t>
+          <t>2271259942</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>6063227845</t>
+          <t>3663535282</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -2373,17 +2373,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12238461185</t>
+          <t>1247665033</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>35</v>
+        <v>252</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -2394,17 +2394,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>3478020599</t>
+          <t>12121829931</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -2415,17 +2415,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1785959222</t>
+          <t>4697885965</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -2436,17 +2436,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1247664991</t>
+          <t>1785959222</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -2457,17 +2457,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1247665033</t>
+          <t>6055482982</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>265</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -2478,17 +2478,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>6055244898</t>
+          <t>1247664991</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -2520,17 +2520,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>4697885965</t>
+          <t>6063227845</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -2541,17 +2541,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>6055482982</t>
+          <t>3478020599</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -2562,17 +2562,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1670386822</t>
+          <t>4289542433</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -2583,17 +2583,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1664599992</t>
+          <t>13134003455</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>0.29</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>541</v>
+        <v>16</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -2604,17 +2604,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>10915994990</t>
+          <t>1670386822</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>384</v>
+        <v>43</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1247665364</t>
+          <t>13131397862</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2646,17 +2646,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>13131397862</t>
+          <t>669224144</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>361</v>
+        <v>46</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -2667,17 +2667,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>9817149191</t>
+          <t>12121806679</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>530</v>
+        <v>346</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>0.02</v>
@@ -2709,17 +2709,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>13134003455</t>
+          <t>13131375762</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2730,17 +2730,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2587043102</t>
+          <t>1664599992</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>421</v>
+        <v>540</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2751,17 +2751,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>4289542433</t>
+          <t>4697920648</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2772,17 +2772,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>4697920648</t>
+          <t>13131375765</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -2793,17 +2793,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1246355167</t>
+          <t>1654424480</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.28</v>
+        <v>0.01</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>527</v>
+        <v>29</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -2814,17 +2814,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>13131375762</t>
+          <t>4696818422</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -2835,17 +2835,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>13134580209</t>
+          <t>7556478690</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>135</v>
+        <v>259</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -2856,17 +2856,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>3663502700</t>
+          <t>1246355167</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>604</v>
+        <v>523</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -2877,17 +2877,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>7556478690</t>
+          <t>1247665364</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>221</v>
+        <v>396</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -2898,17 +2898,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>299632113</t>
+          <t>13131375767</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>416</v>
+        <v>106</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -2919,17 +2919,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>5935647076</t>
+          <t>2587043102</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>503</v>
+        <v>401</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -2940,17 +2940,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>6027310523</t>
+          <t>299632113</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>547</v>
+        <v>451</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -2961,17 +2961,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>6060574286</t>
+          <t>9884618525</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>442</v>
+        <v>655</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -2982,17 +2982,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>13134003460</t>
+          <t>339225135</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>466</v>
+        <v>553</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3003,17 +3003,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>6057106000</t>
+          <t>6055244898</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>669224144</t>
+          <t>6057106000</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -3045,17 +3045,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>9884618525</t>
+          <t>11516632609</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.31</v>
+        <v>0.02</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>655</v>
+        <v>39</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -3066,17 +3066,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>11516632572</t>
+          <t>1246355189</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>538</v>
+        <v>35</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3087,17 +3087,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>11516632609</t>
+          <t>3430028812</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3108,17 +3108,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1246355189</t>
+          <t>5935647076</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.01</v>
+        <v>0.23</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>33</v>
+        <v>517</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3129,17 +3129,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1247665627</t>
+          <t>6060574286</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>28</v>
+        <v>486</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -3150,17 +3150,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>1661742603</t>
+          <t>13134003460</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>23</v>
+        <v>455</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -3171,17 +3171,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>339225135</t>
+          <t>13134580209</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>553</v>
+        <v>134</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -3192,17 +3192,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>3430028812</t>
+          <t>1833486480</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3213,17 +3213,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>4696818416</t>
+          <t>6057358075</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -3234,17 +3234,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>4696818422</t>
+          <t>11516609609</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -3255,17 +3255,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>6057358075</t>
+          <t>1247665021</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>556</v>
+        <v>60</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -3276,17 +3276,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>1169044590</t>
+          <t>1247665627</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>209</v>
+        <v>28</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -3297,17 +3297,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>1247665021</t>
+          <t>1785959154</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>13134003457</t>
+          <t>299639758</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3328,7 +3328,7 @@
         <v>0.01</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -3339,17 +3339,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>10915994985</t>
+          <t>11516632572</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -3360,17 +3360,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11516609609</t>
+          <t>1169044590</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>35</v>
+        <v>223</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -3402,17 +3402,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>12280837959</t>
+          <t>1247665486</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>299633520</t>
+          <t>5526343912</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1</v>
+        <v>452</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -3444,17 +3444,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>3478019144</t>
+          <t>70649445</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -3465,17 +3465,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>5526343912</t>
+          <t>11516632601</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>0.16</v>
+        <v>0.02</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>432</v>
+        <v>44</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -3486,17 +3486,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>70649445</t>
+          <t>12280837959</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -3507,17 +3507,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11516632600</t>
+          <t>1438438595</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -3528,17 +3528,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>1247665101</t>
+          <t>11738664186</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>15</v>
+        <v>508</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -3549,17 +3549,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>12909444338</t>
+          <t>1247664943</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -3570,17 +3570,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13131375767</t>
+          <t>1247665101</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>299639758</t>
+          <t>13134003457</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3612,17 +3612,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>4696835286</t>
+          <t>1654424042</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>521</v>
+        <v>42</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3633,17 +3633,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>11738664186</t>
+          <t>1661742603</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>523</v>
+        <v>26</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3654,17 +3654,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>12121806679</t>
+          <t>1761421863</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>306</v>
+        <v>585</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3675,17 +3675,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>3441398845</t>
+          <t>3663502700</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>8</v>
+        <v>631</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3696,17 +3696,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>4198760294</t>
+          <t>4696818416</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>0.01</v>
+        <v>0.18</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>28</v>
+        <v>529</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>0.01</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3738,17 +3738,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11516632601</t>
+          <t>6027310523</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>32</v>
+        <v>585</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>0.01</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>0.05</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3801,17 +3801,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>13134580212</t>
+          <t>4198760294</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3822,11 +3822,11 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>6047005881</t>
+          <t>4995658236</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="C86" s="2" t="n">
         <v>0.01</v>
@@ -3843,17 +3843,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>13134003461</t>
+          <t>6047005881</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3864,17 +3864,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>3478020616</t>
+          <t>9817149191</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>27</v>
+        <v>530</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3885,17 +3885,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>4995658238</t>
+          <t>10915994985</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3906,17 +3906,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>11919898578</t>
+          <t>13134003456</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>11</v>
+        <v>346</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3927,17 +3927,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13131397858</t>
+          <t>13134003461</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3948,17 +3948,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>13134003463</t>
+          <t>4696835286</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>577</v>
+        <v>523</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3969,17 +3969,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>1761421863</t>
+          <t>10915994990</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>521</v>
+        <v>342</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -3990,17 +3990,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2142757871</t>
+          <t>13131397858</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="C94" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -4011,17 +4011,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2512738716</t>
+          <t>13134580212</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -4032,17 +4032,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>3430028799</t>
+          <t>3478050376</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -4053,17 +4053,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>12909444328</t>
+          <t>12909444338</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -4074,17 +4074,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>1654424042</t>
+          <t>13134580218</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -4095,17 +4095,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2591388559</t>
+          <t>3478053502</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -4116,17 +4116,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>1247664812</t>
+          <t>12909444330</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>30</v>
+        <v>597</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -4137,17 +4137,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>1247665486</t>
+          <t>2142757871</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -4158,17 +4158,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13134003456</t>
+          <t>2512738716</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>366</v>
+        <v>108</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -4179,17 +4179,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>1438438595</t>
+          <t>3430028799</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -4200,17 +4200,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>1654424480</t>
+          <t>3478020616</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>299627271</t>
+          <t>1247664812</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="C105" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4242,17 +4242,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>3478050376</t>
+          <t>13131375764</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C106" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>0.01</v>
-      </c>
       <c r="D106" s="2" t="n">
-        <v>33</v>
+        <v>398</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4263,17 +4263,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11516632582</t>
+          <t>13134003463</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>433</v>
+        <v>610</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -4284,17 +4284,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>12909444330</t>
+          <t>13134580214</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>482</v>
+        <v>11</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4305,17 +4305,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>13131375764</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>380</v>
+        <v>39</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -4326,17 +4326,17 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>13134580218</t>
+          <t>11516632582</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -4347,17 +4347,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>3441398795</t>
+          <t>11919898578</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -4368,17 +4368,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>11738664240</t>
+          <t>299627271</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4389,17 +4389,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>1247665301</t>
+          <t>3441398795</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4410,17 +4410,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>13131375765</t>
+          <t>3441398845</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="C114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4431,17 +4431,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>3478053502</t>
+          <t>3478019144</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="C115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -4452,17 +4452,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>60881778</t>
+          <t>11738664240</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -4473,17 +4473,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>70650627</t>
+          <t>2591388559</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
@@ -4498,13 +4498,13 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
@@ -4515,17 +4515,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>282071079</t>
+          <t>4995658238</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
@@ -4536,17 +4536,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>4995658232</t>
+          <t>1247665301</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="C120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -4557,17 +4557,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>4995658236</t>
+          <t>12909444328</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
@@ -4578,17 +4578,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>11516632573</t>
+          <t>282071079</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C122" s="2" t="n">
         <v>0.02</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>0.01</v>
-      </c>
       <c r="D122" s="2" t="n">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
@@ -4599,17 +4599,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2271259943</t>
+          <t>11738664244</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
@@ -4620,17 +4620,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>6058348491</t>
+          <t>11516632573</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C124" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D124" s="2" t="n">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
@@ -4641,17 +4641,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>2271259943</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
@@ -4662,17 +4662,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>11738664244</t>
+          <t>3478053500</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
@@ -4683,17 +4683,17 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>12121829931</t>
+          <t>6058348491</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>12280837956</t>
+          <t>70650627</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>12280837962</t>
+          <t>12280837956</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -4735,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>1246355176</t>
+          <t>12280837962</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -4756,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>1247664943</t>
+          <t>1246355176</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -4777,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>13134580214</t>
+          <t>13134580215</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>13134580215</t>
+          <t>2281352575</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>1833486480</t>
+          <t>2639664145</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -4998,7 +4998,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2281352575</t>
+          <t>299633520</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -5008,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2639664145</t>
+          <t>3430028802</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
@@ -5029,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>3430028802</t>
+          <t>3478020625</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
@@ -5050,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>3478020625</t>
+          <t>3478050372</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
@@ -5071,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>3478050372</t>
+          <t>3478050391</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
@@ -5092,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>3478050391</t>
+          <t>4696836111</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
@@ -5113,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>3478053500</t>
+          <t>4995658232</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>4696836111</t>
+          <t>5199105790</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>5199105790</t>
+          <t>6047007986</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
@@ -5187,7 +5187,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>6047007986</t>
+          <t>60881778</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
@@ -5197,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
